--- a/ig/DM-OCTOBRE-2024/CodeSystem-TRE-R85-RolePriseCharge.xlsx
+++ b/ig/DM-OCTOBRE-2024/CodeSystem-TRE-R85-RolePriseCharge.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="212">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240329120000</t>
+    <t>20241025120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T12:00:00+01:00</t>
+    <t>2024-10-25T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -412,7 +412,7 @@
     <t>331</t>
   </si>
   <si>
-    <t>Secrétaire médicale</t>
+    <t>Secrétaire assistante médico-administrative</t>
   </si>
   <si>
     <t>332</t>
@@ -439,6 +439,90 @@
     <t>Gestionnaire alertes et urgences sanitaires</t>
   </si>
   <si>
+    <t>336</t>
+  </si>
+  <si>
+    <t>Autre professionnel intervenant dans l'accueil et l'orientation des personnes</t>
+  </si>
+  <si>
+    <t>337</t>
+  </si>
+  <si>
+    <t>Autre professionnel intervenant dans la logistique</t>
+  </si>
+  <si>
+    <t>338</t>
+  </si>
+  <si>
+    <t>Autre professionnel intervenant dans l'hôtellerie et la restauration</t>
+  </si>
+  <si>
+    <t>339</t>
+  </si>
+  <si>
+    <t>Autre professionnel de la qualité, hygiène, sécurité et environnement</t>
+  </si>
+  <si>
+    <t>340</t>
+  </si>
+  <si>
+    <t>Autre professionnel intervenant dans la direction des systèmes d'information</t>
+  </si>
+  <si>
+    <t>341</t>
+  </si>
+  <si>
+    <t>Autre professionnel intervenant dans la direction des finances et comptabilité</t>
+  </si>
+  <si>
+    <t>342</t>
+  </si>
+  <si>
+    <t>Autre professionnel intervenant dans la direction de la communication</t>
+  </si>
+  <si>
+    <t>343</t>
+  </si>
+  <si>
+    <t>Autre professionnel intervenant dans la direction des ressources humaines</t>
+  </si>
+  <si>
+    <t>344</t>
+  </si>
+  <si>
+    <t>Autre professionnel intervenant dans la direction des affaires médicales</t>
+  </si>
+  <si>
+    <t>345</t>
+  </si>
+  <si>
+    <t>Autre professionnel intervenant dans le social, éducatif, psychologie et culturel</t>
+  </si>
+  <si>
+    <t>346</t>
+  </si>
+  <si>
+    <t>Etudiant - infirmier</t>
+  </si>
+  <si>
+    <t>347</t>
+  </si>
+  <si>
+    <t>Etudiant - aide-soignant</t>
+  </si>
+  <si>
+    <t>348</t>
+  </si>
+  <si>
+    <t>Etudiant - auxiliaire de puériculture</t>
+  </si>
+  <si>
+    <t>349</t>
+  </si>
+  <si>
+    <t>Etudiant - masseur-kinésithérapeute</t>
+  </si>
+  <si>
     <t>350</t>
   </si>
   <si>
@@ -464,6 +548,108 @@
   </si>
   <si>
     <t>Membre de l'équipe de soins</t>
+  </si>
+  <si>
+    <t>354</t>
+  </si>
+  <si>
+    <t>Externe en médecine</t>
+  </si>
+  <si>
+    <t>355</t>
+  </si>
+  <si>
+    <t>Externe en odontologie</t>
+  </si>
+  <si>
+    <t>356</t>
+  </si>
+  <si>
+    <t>Externe en maïeutique</t>
+  </si>
+  <si>
+    <t>357</t>
+  </si>
+  <si>
+    <t>Externe en pharmacie</t>
+  </si>
+  <si>
+    <t>358</t>
+  </si>
+  <si>
+    <t>Autre étudiant</t>
+  </si>
+  <si>
+    <t>359</t>
+  </si>
+  <si>
+    <t>Directeur d'établissement</t>
+  </si>
+  <si>
+    <t>360</t>
+  </si>
+  <si>
+    <t>Brancardier</t>
+  </si>
+  <si>
+    <t>361</t>
+  </si>
+  <si>
+    <t>Educateur en activité physique adaptée</t>
+  </si>
+  <si>
+    <t>362</t>
+  </si>
+  <si>
+    <t>Technicien d'informations médicales</t>
+  </si>
+  <si>
+    <t>363</t>
+  </si>
+  <si>
+    <t>Attaché de recherche clinique</t>
+  </si>
+  <si>
+    <t>364</t>
+  </si>
+  <si>
+    <t>Praticien A Diplôme Hors Union Européenne (PADHUE)</t>
+  </si>
+  <si>
+    <t>365</t>
+  </si>
+  <si>
+    <t>Gestionnaire admissions / frais de séjour / traitement externe</t>
+  </si>
+  <si>
+    <t>366</t>
+  </si>
+  <si>
+    <t>Archiviste</t>
+  </si>
+  <si>
+    <t>367</t>
+  </si>
+  <si>
+    <t>Surveillant de nuit</t>
+  </si>
+  <si>
+    <t>368</t>
+  </si>
+  <si>
+    <t>Animateur</t>
+  </si>
+  <si>
+    <t>369</t>
+  </si>
+  <si>
+    <t>Biologiste médical non-médecin</t>
+  </si>
+  <si>
+    <t>370</t>
+  </si>
+  <si>
+    <t>Opérateur de Soins Non Programmés (OSNP)</t>
   </si>
 </sst>
 </file>
@@ -837,7 +1023,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1334,19 +1520,17 @@
       <c r="C38" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="D38" t="s" s="2">
-        <v>143</v>
-      </c>
+      <c r="D38" s="2"/>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B39" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="C39" t="s" s="2">
         <v>144</v>
-      </c>
-      <c r="C39" t="s" s="2">
-        <v>145</v>
       </c>
       <c r="D39" s="2"/>
     </row>
@@ -1355,10 +1539,10 @@
         <v>49</v>
       </c>
       <c r="B40" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="C40" t="s" s="2">
         <v>146</v>
-      </c>
-      <c r="C40" t="s" s="2">
-        <v>147</v>
       </c>
       <c r="D40" s="2"/>
     </row>
@@ -1367,12 +1551,386 @@
         <v>49</v>
       </c>
       <c r="B41" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="C41" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="C41" t="s" s="2">
+      <c r="D41" s="2"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B42" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="D41" s="2"/>
+      <c r="C42" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="D42" s="2"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="C43" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="D43" s="2"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="D44" s="2"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="C45" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="D45" s="2"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="C46" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="D46" s="2"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="C47" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="D47" s="2"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="D48" s="2"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="D49" s="2"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="C50" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="D50" s="2"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="C51" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="D51" s="2"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="C52" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="D52" t="s" s="2">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="C53" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="D53" s="2"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="C54" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="D54" s="2"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="C55" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="D55" s="2"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="C56" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="D56" s="2"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="D57" s="2"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="C58" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="D58" s="2"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="C59" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="D59" s="2"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="C60" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="D60" s="2"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="C61" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="D61" s="2"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="C62" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="D62" s="2"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="C63" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="D63" s="2"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="C64" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="D64" s="2"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="C65" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="D65" s="2"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="C66" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="D66" s="2"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="C67" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="D67" s="2"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="C68" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="D68" s="2"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="C69" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="D69" s="2"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="C70" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="D70" s="2"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="C71" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="D71" s="2"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="C72" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="D72" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
